--- a/_Drive/Publicacoes/jacare.xlsx
+++ b/_Drive/Publicacoes/jacare.xlsx
@@ -4,7 +4,7 @@
   <fileVersion lastEdited="4" lowestEdited="4" rupBuild="3820"/>
   <workbookPr date1904="0"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView activeTab="0" windowWidth="14400" windowHeight="6300"/>
   </bookViews>
   <sheets>
     <sheet name="jacare.doi" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,227 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67" count="67">
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-010-9846-x</t>
+  </si>
+  <si>
+    <t>10.1021/ic401413f</t>
+  </si>
+  <si>
+    <t>10.1016/j.ijrmhm.2012.04.008</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-020-00787-4</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2006.08.159</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2010.08.019</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-008-9390-0</t>
+  </si>
+  <si>
+    <t>10.1016/j.intermet.2006.10.054</t>
+  </si>
+  <si>
+    <t>10.1361/105497103770330758</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2019.06.186</t>
+  </si>
+  <si>
+    <t>10.1016/j.mtcomm.2020.101282</t>
+  </si>
+  <si>
+    <t>10.1007/s11665-013-0531-1</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-020-00819-z</t>
+  </si>
+  <si>
+    <t>10.1016/j.calphad.2020.102196</t>
+  </si>
+  <si>
+    <t>10.1007/s11085-014-9517-0</t>
+  </si>
+  <si>
+    <t>10.1016/j.calphad.2019.101676</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2018.09.139</t>
+  </si>
+  <si>
+    <t>10.1016/j.surfcoat.2020.125675</t>
+  </si>
+  <si>
+    <t>10.1016/j.matchar.2006.05.014</t>
+  </si>
+  <si>
+    <t>10.1016/j.calphad.2017.10.001</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-009-9533-y</t>
+  </si>
+  <si>
+    <t>10.1007/s11665-013-0814-6</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-015-0418-y</t>
+  </si>
+  <si>
+    <t>10.3390/met9050589</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-009-9610-2</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2014.07.026</t>
+  </si>
+  <si>
+    <t>10.1016/j.matchar.2005.10.001</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2013.04.070</t>
+  </si>
+  <si>
+    <t>10.1016/j.intermet.2009.03.006</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-020-00838-w</t>
+  </si>
+  <si>
+    <t>10.1109/TMAG.2009.2033460</t>
+  </si>
+  <si>
+    <t>10.1016/j.corsci.2019.108165</t>
+  </si>
+  <si>
+    <t>10.1016/j.ijrmhm.2011.06.012</t>
+  </si>
+  <si>
+    <t>10.4028/www.scientific.net/MSF.416-418.251</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2003.09.117</t>
+  </si>
+  <si>
+    <t>10.1007/s11665-013-0565-4</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-020-00802-8</t>
+  </si>
+  <si>
+    <t>10.1080/00084433.2017.1409946</t>
+  </si>
+  <si>
+    <t>10.1016/j.jssc.2012.02.009</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-015-0374-6</t>
+  </si>
+  <si>
+    <t>10.1016/j.intermet.2005.05.007</t>
+  </si>
+  <si>
+    <t>10.1016/j.calphad.2018.08.012</t>
+  </si>
+  <si>
+    <t>10.1007/s11085-020-10013-8</t>
+  </si>
+  <si>
+    <t>10.1016/j.jmmm.2009.03.067</t>
+  </si>
+  <si>
+    <t>10.1016/j.scriptamat.2021.113854</t>
+  </si>
+  <si>
+    <t>10.1016/j.matchar.2006.10.020</t>
+  </si>
+  <si>
+    <t>10.1016/j.matchar.2006.10.015</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-014-0330-x</t>
+  </si>
+  <si>
+    <t>10.1590/s1516-14392014005000018</t>
+  </si>
+  <si>
+    <t>10.1016/j.intermet.2003.09.015</t>
+  </si>
+  <si>
+    <t>10.1016/j.matchar.2005.09.009</t>
+  </si>
+  <si>
+    <t>10.1016/j.intermet.2006.05.016</t>
+  </si>
+  <si>
+    <t>10.1590/S1516-14392012005000015</t>
+  </si>
+  <si>
+    <t>10.1016/j.jssc.2012.01.060</t>
+  </si>
+  <si>
+    <t>10.1016/j.matchar.2008.04.002</t>
+  </si>
+  <si>
+    <t>10.1016/j.intermet.2004.01.001</t>
+  </si>
+  <si>
+    <t>10.1016/j.intermet.2016.04.006</t>
+  </si>
+  <si>
+    <t>10.1016/j.actamat.2005.04.020</t>
+  </si>
+  <si>
+    <t>10.1590/1980-5373-MR-2016-0001</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2011.02.042</t>
+  </si>
+  <si>
+    <t>10.1080/00084433.2017.1299907</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2020.156463</t>
+  </si>
+  <si>
+    <t>10.1088/0953-2048/28/9/095016</t>
+  </si>
+  <si>
+    <t>10.1590/1980-5373-mr-2019-0305</t>
+  </si>
+  <si>
+    <t>10.1016/s0263-4368(99)00021-9</t>
+  </si>
+  <si>
+    <t>10.1016/j.matchar.2012.11.006</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <u val="none"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
+      <vertAlign val="baseline"/>
+      <sz val="10"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <u val="none"/>
       <color rgb="FF000000"/>
@@ -62,8 +278,12 @@
       <protection locked="1" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -76,924 +296,798 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A131"/>
+  <dimension ref="A1:A132"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="256" style="0" width="9.142307692307693"/>
+    <col min="1" max="1" style="0" width="38.283413461538466" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" style="0" width="9.142307692307693"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-010-9846-x</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>10.1002/3527607285.ch54</t>
-        </is>
+      <c r="A2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.1007/BF0273644</t>
+          <t>10.1002/3527607285.ch54</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.1021/ic401413f</t>
+          <t>10.1007/BF0273644</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10.1016/j.ijrmhm.2012.04.008</t>
-        </is>
+      <c r="A5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-020-00787-4</t>
-        </is>
+      <c r="A6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10.3139/146.111952</t>
-        </is>
+      <c r="A7" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2006.08.159</t>
+          <t>10.3139/146.111952</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2010.08.019</t>
-        </is>
+      <c r="A9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-008-9390-0</t>
-        </is>
+      <c r="A10" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10.1016/j.intermet.2006.10.054</t>
-        </is>
+      <c r="A11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10.1361/105497103770330758</t>
-        </is>
+      <c r="A12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>10.1016/s0966-9795(02)00125-5</t>
-        </is>
+      <c r="A13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2019.06.186</t>
+          <t>10.1016/s0966-9795(02)00125-5</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2019.04.172</t>
-        </is>
+      <c r="A15" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1016/s1044-5803(01)00176-0</t>
+          <t>10.1016/j.jallcom.2019.04.172</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1016/j.mtcomm.2020.101282</t>
+          <t>10.1016/s1044-5803(01)00176-0</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>10.1088/0953-2048/16/4/317</t>
-        </is>
+      <c r="A18" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1007/s40430-018-1375-2</t>
+          <t>10.1088/0953-2048/16/4/317</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2012.10.016</t>
+          <t>10.1007/s40430-018-1375-2</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1016/j.mtcomm.2019.100767</t>
+          <t>10.1016/j.jallcom.2012.10.016</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.1016/s0263-4368(00)00020-2</t>
+          <t>10.1016/j.mtcomm.2019.100767</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.1007/s11665-013-0531-1</t>
+          <t>10.1016/s0263-4368(00)00020-2</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-020-00819-z</t>
-        </is>
+      <c r="A24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10.1016/j.calphad.2020.102196</t>
-        </is>
+      <c r="A25" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>10.5539/jmsr.v9n1p32</t>
-        </is>
+      <c r="A26" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.802.20</t>
+          <t>10.5539/jmsr.v9n1p32</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.1007/s11665-018-3699-6</t>
+          <t>10.4028/www.scientific.net/msf.802.20</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1590/1980-5373-mr-2019-0178</t>
+          <t>10.1007/s11665-018-3699-6</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2019.05.196</t>
+          <t>10.1590/1980-5373-mr-2019-0178</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.5006/1.3585276</t>
+          <t>10.1016/j.jallcom.2019.05.196</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.1007/s11085-014-9517-0</t>
+          <t>10.5006/1.3585276</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>10.1590/1980-5373-mr-2017-0468</t>
-        </is>
+      <c r="A33" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10.1016/j.calphad.2019.101676</t>
+          <t>10.1590/1980-5373-mr-2017-0468</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2018.09.139</t>
-        </is>
+      <c r="A35" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>10.1016/j.surfcoat.2020.125675</t>
-        </is>
+      <c r="A36" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2011.11.035</t>
-        </is>
+      <c r="A37" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10.1007/s11661-021-06252-2</t>
+          <t>10.1016/j.jallcom.2011.11.035</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2006.05.014</t>
+          <t>10.1007/s11661-021-06252-2</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>10.1590/1980-5373-mr-2017-0637</t>
-        </is>
+      <c r="A40" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10.1016/j.ssc.2011.07.005</t>
+          <t>10.1590/1980-5373-mr-2017-0637</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10.1590/s1516-14392010000300009</t>
+          <t>10.1016/j.ssc.2011.07.005</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10.1016/j.calphad.2017.10.001</t>
+          <t>10.1590/s1516-14392010000300009</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-009-9533-y</t>
-        </is>
+      <c r="A44" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>10.1007/s11665-013-0814-6</t>
-        </is>
+      <c r="A45" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-015-0418-y</t>
-        </is>
+      <c r="A46" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>10.1016/j.msea.2006.02.024</t>
-        </is>
+      <c r="A47" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10.1590/1980-5373-mr-2017-0332</t>
+          <t>10.1016/j.msea.2006.02.024</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/jmnm.20-21.139</t>
+          <t>10.1590/1980-5373-mr-2017-0332</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10.3390/met9050589</t>
+          <t>10.4028/www.scientific.net/jmnm.20-21.139</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-009-9610-2</t>
-        </is>
+      <c r="A51" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>10.1016/j.msec.2013.04.015</t>
-        </is>
+      <c r="A52" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2014.07.026</t>
+          <t>10.1016/j.msec.2013.04.015</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>10.4028/www.scientific.net/MSF.660-661.405</t>
-        </is>
+      <c r="A54" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10.1016/j.jmatprotec.2018.07.034</t>
+          <t>10.4028/www.scientific.net/MSF.660-661.405</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10.1016/S0263-4368(00)00021-4</t>
+          <t>10.1016/j.jmatprotec.2018.07.034</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2005.10.001</t>
+          <t>10.1016/S0263-4368(00)00021-4</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>10.4028/www.scientific.net/msf.802.9</t>
-        </is>
+      <c r="A58" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2013.04.070</t>
+          <t>10.4028/www.scientific.net/msf.802.9</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>10.1016/S1003-6326(18)64867-8</t>
-        </is>
+      <c r="A60" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.1016/j.intermet.2009.03.006</t>
+          <t>10.1016/S1003-6326(18)64867-8</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-020-00838-w</t>
-        </is>
+      <c r="A62" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>10.1109/TMAG.2009.2033460</t>
-        </is>
+      <c r="A63" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>10.1016/j.corsci.2019.108165</t>
-        </is>
+      <c r="A64" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>10.1016/S0966-9795(99)00088-6</t>
-        </is>
+      <c r="A65" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10.1590/s1516-14392013005000172</t>
+          <t>10.1016/S0966-9795(99)00088-6</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10.1016/j.ijrmhm.2011.06.012</t>
+          <t>10.1590/s1516-14392013005000172</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>10.1590/1516-1439.343514</t>
-        </is>
+      <c r="A68" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.416-418.251</t>
+          <t>10.1590/1516-1439.343514</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2003.09.117</t>
-        </is>
+      <c r="A70" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>10.1016/j.msea.2018.05.078</t>
-        </is>
+      <c r="A71" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.1007/s11661-013-1607-0</t>
+          <t>10.1016/j.msea.2018.05.078</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10.1007/s11665-013-0565-4</t>
+          <t>10.1007/s11661-013-1607-0</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-020-00802-8</t>
-        </is>
+      <c r="A74" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>10.1080/00084433.2017.1409946</t>
-        </is>
+      <c r="A75" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>10.1016/j.jssc.2012.02.009</t>
-        </is>
+      <c r="A76" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>10.1007/s11665-019-04014-1</t>
-        </is>
+      <c r="A77" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10.1007/s11669-015-0374-6</t>
+          <t>10.1007/s11665-019-04014-1</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2014.01.173</t>
-        </is>
+      <c r="A79" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10.1016/j.intermet.2005.05.007</t>
+          <t>10.1016/j.jallcom.2014.01.173</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>10.1016/j.calphad.2018.08.012</t>
-        </is>
+      <c r="A81" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>10.1007/s11085-020-10013-8</t>
-        </is>
+      <c r="A82" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>10.1016/j.jmmm.2009.03.067</t>
-        </is>
+      <c r="A83" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>10.1016/j.scriptamat.2021.113854</t>
-        </is>
+      <c r="A84" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>10.1016/j.matchar.2006.10.020</t>
-        </is>
+      <c r="A85" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>10.1007/s11665-016-2051-2</t>
-        </is>
+      <c r="A86" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2021.141170</t>
+          <t>10.1007/s11665-016-2051-2</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2006.10.015</t>
+          <t>10.1016/j.msea.2021.141170</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-001-0074-2</t>
-        </is>
+      <c r="A89" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10.1016/j.ijrmhm.2005.06.001</t>
+          <t>10.1007/s11669-001-0074-2</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10.1007/s11669-014-0330-x</t>
+          <t>10.1016/j.ijrmhm.2005.06.001</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>10.1016/j.jmrt.2018.12.020</t>
-        </is>
+      <c r="A92" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10.1590/s1516-14392014005000018</t>
+          <t>10.1016/j.jmrt.2018.12.020</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>10.1016/j.intermet.2003.09.015</t>
-        </is>
+      <c r="A94" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>10.1016/j.matchar.2005.09.009</t>
-        </is>
+      <c r="A95" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>10.1016/j.intermet.2006.05.016</t>
-        </is>
+      <c r="A96" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>10.1590/S1516-14392012005000015</t>
-        </is>
+      <c r="A97" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>10.1016/j.jssc.2012.01.060</t>
-        </is>
+      <c r="A98" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>10.4028/www.scientific.net/jmnm.20-21.145</t>
-        </is>
+      <c r="A99" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10.1016/j.ssc.2008.12.037</t>
+          <t>10.4028/www.scientific.net/jmnm.20-21.145</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2008.04.002</t>
+          <t>10.1016/j.ssc.2008.12.037</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>10.1016/j.intermet.2004.01.001</t>
-        </is>
+      <c r="A102" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>10.1007/s11665-016-2462-0</t>
-        </is>
+      <c r="A103" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10.1016/j.intermet.2016.04.006</t>
+          <t>10.1007/s11665-016-2462-0</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>10.1016/j.actamat.2005.04.020</t>
-        </is>
+      <c r="A105" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>10.1590/1980-5373-MR-2016-0001</t>
-        </is>
+      <c r="A106" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>10.1016/s0039-9140(02)00471-x</t>
-        </is>
+      <c r="A107" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10.1016/j.ijrmhm.2010.09.006</t>
+          <t>10.1016/s0039-9140(02)00471-x</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/JMNM.20-21.201</t>
+          <t>10.1016/j.ijrmhm.2010.09.006</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2011.02.042</t>
+          <t>10.4028/www.scientific.net/JMNM.20-21.201</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>10.1016/s0921-5093(03)00650-6</t>
-        </is>
+      <c r="A111" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10.1080/00084433.2017.1299907</t>
+          <t>10.1016/s0921-5093(03)00650-6</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2020.156463</t>
-        </is>
+      <c r="A113" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>10.3390/met8020082</t>
-        </is>
+      <c r="A114" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/28/9/095016</t>
+          <t>10.3390/met8020082</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>10.1016/S0263-4368(99)00002-5</t>
-        </is>
+      <c r="A116" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2014.02.179</t>
+          <t>10.1016/S0263-4368(99)00002-5</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10.1016/s0966-9795(02)00249-2</t>
+          <t>10.1016/j.jallcom.2014.02.179</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10.1590/1980-5373-mr-2019-0305</t>
+          <t>10.1016/s0966-9795(02)00249-2</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>10.1590/1516-1439.329614</t>
-        </is>
+      <c r="A120" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>10.1007/s11669-004-0006-z</t>
+          <t>10.1590/1516-1439.329614</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10.1111/j.1525-1594.2008.00546.x</t>
+          <t>10.1007/s11669-004-0006-z</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10.1590/1980-5373-mr-2019-0599</t>
+          <t>10.1111/j.1525-1594.2008.00546.x</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>10.1016/s0263-4368(99)00021-9</t>
+          <t>10.1590/1980-5373-mr-2019-0599</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>10.4028/www.scientific.net/msf.805.199</t>
-        </is>
+      <c r="A125" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.869.952</t>
+          <t>10.4028/www.scientific.net/msf.805.199</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10.1016/j.surfcoat.2021.126999</t>
+          <t>10.4028/www.scientific.net/MSF.869.952</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.660-661.152</t>
+          <t>10.1016/j.surfcoat.2021.126999</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2012.11.006</t>
+          <t>10.4028/www.scientific.net/MSF.660-661.152</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2011.09.081</t>
-        </is>
+      <c r="A130" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="inlineStr">
+        <is>
+          <t>10.1016/j.jallcom.2011.09.081</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>10.1007/978-3-319-19443-1_24</t>
         </is>
